--- a/data/trans_dic/IP16B01-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP16B01-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos recetados por el médico para el catarro, gripe, garganta, bronquios</t>
+          <t>Menores que consumiero medicamentos recetados por el médico para el catarro, gripe, garganta, bronquios (tasa de respuesta: 99,34%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 5,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>58,96; 94,73</t>
+          <t>58,8; 94,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47,81; 100,0</t>
+          <t>52,67; 100,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 6,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>65,39; 100,0</t>
+          <t>62,55; 100,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>54,47; 100,0</t>
+          <t>53,64; 100,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>68,65; 92,64</t>
+          <t>65,5; 92,6</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>66,08; 95,57</t>
+          <t>64,97; 95,46</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,24</t>
+          <t>0,0; 4,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>75,0; 90,94</t>
+          <t>74,82; 91,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>68,78; 88,08</t>
+          <t>68,1; 87,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,44</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>90,14; 99,01</t>
+          <t>89,69; 98,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>79,59; 95,21</t>
+          <t>79,59; 95,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,27</t>
+          <t>0,0; 2,11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>85,64; 94,28</t>
+          <t>84,97; 93,85</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>76,57; 89,58</t>
+          <t>76,69; 89,26</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,39</t>
+          <t>0,0; 14,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>62,59; 90,77</t>
+          <t>64,81; 91,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>71,29; 96,41</t>
+          <t>70,87; 96,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>75,92; 97,31</t>
+          <t>77,58; 97,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>64,54; 95,56</t>
+          <t>63,62; 95,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,06</t>
+          <t>0,0; 6,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>75,57; 92,24</t>
+          <t>74,38; 92,49</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>75,15; 95,48</t>
+          <t>74,14; 93,92</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,51</t>
+          <t>0,0; 3,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>75,19; 88,06</t>
+          <t>75,35; 88,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>73,73; 88,63</t>
+          <t>73,88; 87,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,89</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>87,87; 96,99</t>
+          <t>88,05; 97,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,16; 93,98</t>
+          <t>80,09; 93,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,77</t>
+          <t>0,0; 1,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>83,68; 91,27</t>
+          <t>83,55; 91,28</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>80,18; 89,58</t>
+          <t>79,58; 89,15</t>
         </is>
       </c>
     </row>
@@ -1071,4 +1072,791 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero medicamentos recetados por el médico para el catarro, gripe, garganta, bronquios (tasa de respuesta: 99,34%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>10850</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>7822</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>9939</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>5726</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>20789</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>13548</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>8005; 12903</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>4954; 9406</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>7073; 11308</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>3454; 6439</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>16326; 23080</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>10294; 15124</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>707</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>50201</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>38924</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>58588</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>41308</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>707</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>108789</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>80233</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3548</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>44562; 54253</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>33529; 43057</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>54893; 60560</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>36894; 44238</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3554</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>102615; 113336</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>73305; 85323</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>19822</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>15671</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>23927</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>11946</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>43750</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>27617</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3228</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>16224; 22872</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>12582; 17089</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>20510; 25742</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>8899; 13362</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3853</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>38281; 47603</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>23532; 29813</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>1349</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>80874</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>62418</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>92453</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>58981</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1349</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>173326</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>121399</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4707</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>73996; 86422</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>56439; 67099</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>87123; 96011</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>53488; 62610</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4663</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>164724; 179957</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>113939; 127644</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16B01-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP16B01-Estudios-trans_dic.xlsx
@@ -683,12 +683,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>58,8; 94,77</t>
+          <t>59,18; 95,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52,67; 100,0</t>
+          <t>49,7; 100,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -698,12 +698,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>62,55; 100,0</t>
+          <t>64,85; 100,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>53,64; 100,0</t>
+          <t>53,72; 100,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>65,5; 92,6</t>
+          <t>67,45; 94,01</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>64,97; 95,46</t>
+          <t>64,9; 95,75</t>
         </is>
       </c>
     </row>
@@ -788,17 +788,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,4</t>
+          <t>0,0; 4,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>74,82; 91,09</t>
+          <t>75,65; 90,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>68,1; 87,45</t>
+          <t>67,55; 87,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -808,27 +808,27 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>89,69; 98,95</t>
+          <t>89,09; 98,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>79,59; 95,43</t>
+          <t>78,85; 95,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,11</t>
+          <t>0,0; 2,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>84,97; 93,85</t>
+          <t>85,29; 93,97</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>76,69; 89,26</t>
+          <t>76,91; 89,73</t>
         </is>
       </c>
     </row>
@@ -898,17 +898,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,31</t>
+          <t>0,0; 14,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>64,81; 91,37</t>
+          <t>61,31; 90,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>70,87; 96,26</t>
+          <t>70,54; 96,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -918,27 +918,27 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>77,58; 97,38</t>
+          <t>75,41; 97,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>63,62; 95,52</t>
+          <t>60,98; 95,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,66</t>
+          <t>0,0; 6,39</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>74,38; 92,49</t>
+          <t>75,51; 92,48</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>74,14; 93,92</t>
+          <t>75,62; 95,38</t>
         </is>
       </c>
     </row>
@@ -1008,17 +1008,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,76</t>
+          <t>0,0; 3,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>75,35; 88,0</t>
+          <t>75,02; 87,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>73,88; 87,83</t>
+          <t>73,09; 87,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>88,05; 97,03</t>
+          <t>87,96; 96,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,09; 93,75</t>
+          <t>80,18; 93,61</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>83,55; 91,28</t>
+          <t>83,82; 91,34</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>79,58; 89,15</t>
+          <t>79,46; 89,31</t>
         </is>
       </c>
     </row>
@@ -1311,12 +1311,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8005; 12903</t>
+          <t>8057; 12956</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4954; 9406</t>
+          <t>4675; 9406</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1326,12 +1326,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7073; 11308</t>
+          <t>7333; 11308</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3454; 6439</t>
+          <t>3459; 6439</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1341,12 +1341,12 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16326; 23080</t>
+          <t>16810; 23429</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10294; 15124</t>
+          <t>10283; 15170</t>
         </is>
       </c>
     </row>
@@ -1469,17 +1469,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3548</t>
+          <t>0; 3532</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>44562; 54253</t>
+          <t>45056; 54133</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>33529; 43057</t>
+          <t>33256; 43103</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1489,27 +1489,27 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>54893; 60560</t>
+          <t>54526; 60411</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36894; 44238</t>
+          <t>36550; 44237</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3554</t>
+          <t>0; 4082</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>102615; 113336</t>
+          <t>102995; 113478</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>73305; 85323</t>
+          <t>73522; 85775</t>
         </is>
       </c>
     </row>
@@ -1632,17 +1632,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3228</t>
+          <t>0; 3223</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>16224; 22872</t>
+          <t>15348; 22702</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12582; 17089</t>
+          <t>12523; 17101</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1652,27 +1652,27 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>20510; 25742</t>
+          <t>19935; 25698</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8899; 13362</t>
+          <t>8531; 13355</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3853</t>
+          <t>0; 3694</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>38281; 47603</t>
+          <t>38863; 47595</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>23532; 29813</t>
+          <t>24004; 30276</t>
         </is>
       </c>
     </row>
@@ -1795,17 +1795,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4707</t>
+          <t>0; 4725</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>73996; 86422</t>
+          <t>73677; 86225</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>56439; 67099</t>
+          <t>55837; 67045</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1815,27 +1815,27 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>87123; 96011</t>
+          <t>87037; 95751</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>53488; 62610</t>
+          <t>53546; 62516</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4663</t>
+          <t>0; 4669</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>164724; 179957</t>
+          <t>165258; 180086</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>113939; 127644</t>
+          <t>113767; 127868</t>
         </is>
       </c>
     </row>
